--- a/hardware/bom/RescueSwarm_BOM.xlsx
+++ b/hardware/bom/RescueSwarm_BOM.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -96,8 +96,16 @@
       <color rgb="FF0000FF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -126,6 +134,16 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -163,7 +181,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -371,6 +389,12 @@
     </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -625,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B2:C22"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="35" min="1" max="1"/>
@@ -633,220 +657,242 @@
     <col width="90" customWidth="1" style="35" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="2" ht="17.35" customHeight="1" s="36">
-      <c r="B2" s="37" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="36">
+      <c r="A1" s="70" t="inlineStr">
+        <is>
+          <t>SUPERSEDED - DO NOT QUOTE THESE FIGURES</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" s="36">
+      <c r="A2" s="71" t="inlineStr">
+        <is>
+          <t>The live budget is RescueSwarm_Cost_Study.xlsx (ask 737,829, 7.38 L), generated from docs/proposal/figures/competition_budget.py. The original pre-India costing. Superseded twice over.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" s="36"/>
+    <row r="5" ht="27.75" customHeight="1" s="36"/>
+    <row r="6" ht="39" customHeight="1" s="36">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>RescueSwarm — Complete Bill of Materials</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="36">
-      <c r="B3" s="38" t="inlineStr">
+    <row r="7" ht="64.5" customHeight="1" s="36">
+      <c r="B7" s="38" t="inlineStr">
         <is>
           <t>NIDAR 2026–27 Track 1 · derived from the Sizing &amp; Calculations report</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="27.75" customHeight="1" s="36">
-      <c r="B5" s="39" t="inlineStr">
-        <is>
-          <t>PURPOSE</t>
-        </is>
-      </c>
-      <c r="C5" s="40" t="inlineStr">
-        <is>
-          <t>Every component required to build the 3-aircraft RescueSwarm system, the ground segment, the test rig, and the spares. Quantities and masses are traceable to the sizing model.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="39" customHeight="1" s="36">
-      <c r="B6" s="39" t="inlineStr">
-        <is>
-          <t>DESIGN POINT</t>
-        </is>
-      </c>
-      <c r="C6" s="40" t="inlineStr">
-        <is>
-          <t>Quadrotor · 18x6.1 CF folding props · T-Motor MN5008 KV170 · 6S3P 21700 Li-ion (18 cells, 292 Wh) · MTOW 5.71 kg · fleet 17.12 kg against a 25 kg cap (32% margin) · hover 784 W · endurance 17.9 min vs a 7.7 min design mission (2.3x).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="64.5" customHeight="1" s="36">
-      <c r="B7" s="39" t="inlineStr">
-        <is>
-          <t>CHANGE FROM THE SIZING REPORT</t>
-        </is>
-      </c>
-      <c r="C7" s="40" t="inlineStr">
-        <is>
-          <t>The report assumed 20 in props and a 6S2P pack. Real hardware forced two revisions: (1) the MN5008 is rated for 17-18 in props, so the baseline moves to 18x6.1 (hover power 666 W instead of 605 W); (2) 6S2P left only 9% current margin at peak thrust, so the pack goes to 6S3P. Both changes are documented on the Mass Rollup tab. MTOW rises 5.05 -&gt; 5.71 kg; the fleet is still 32% under the cap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="39" customHeight="1" s="36">
-      <c r="B8" s="39" t="inlineStr">
-        <is>
-          <t>PRICES</t>
-        </is>
-      </c>
-      <c r="C8" s="40" t="inlineStr">
-        <is>
-          <t>INDICATIVE BUDGETARY ESTIMATES IN INR, for planning only. They are not quotations. Import duty, GST and freight are added as separate lines on the Cost Summary. Re-price everything at the Phase 1 procurement gate.</t>
-        </is>
-      </c>
-    </row>
+    <row r="8" ht="39" customHeight="1" s="36"/>
     <row r="9" ht="39" customHeight="1" s="36">
       <c r="B9" s="39" t="inlineStr">
         <is>
-          <t>MASSES</t>
+          <t>PURPOSE</t>
         </is>
       </c>
       <c r="C9" s="40" t="inlineStr">
         <is>
-          <t>Manufacturer figures where published (marked in the Source column); otherwise engineering estimates. Weigh every part on arrival and update the Actual Mass column — the fleet weigh-in is a pass/fail rule check.</t>
+          <t>Every component required to build the 3-aircraft RescueSwarm system, the ground segment, the test rig, and the spares. Quantities and masses are traceable to the sizing model.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="39" customHeight="1" s="36">
       <c r="B10" s="39" t="inlineStr">
         <is>
-          <t>HOW TO USE</t>
+          <t>DESIGN POINT</t>
         </is>
       </c>
       <c r="C10" s="40" t="inlineStr">
         <is>
-          <t>Blue cells are inputs you should edit. Black cells are formulas. Yellow cells are decisions still open. Fill the "Actual Mass" and "Actual Price" columns as parts arrive; the Mass Rollup and Cost Summary update automatically.</t>
+          <t>Quadrotor · 18x6.1 CF folding props · T-Motor MN5008 KV170 · 6S3P 21700 Li-ion (18 cells, 292 Wh) · MTOW 5.71 kg · fleet 17.12 kg against a 25 kg cap (32% margin) · hover 784 W · endurance 17.9 min vs a 7.7 min design mission (2.3x).</t>
         </is>
       </c>
     </row>
     <row r="11" ht="39" customHeight="1" s="36">
       <c r="B11" s="39" t="inlineStr">
         <is>
-          <t>TIERS</t>
+          <t>CHANGE FROM THE SIZING REPORT</t>
         </is>
       </c>
       <c r="C11" s="40" t="inlineStr">
         <is>
-          <t>Where a component has a wide price range (mesh radio, compute, GNSS), three options are listed: A = student budget, B = mid, C = professional. Tier A is costed in the totals. Swapping tiers only requires changing the Include column to 1/0.</t>
+          <t>The report assumed 20 in props and a 6S2P pack. Real hardware forced two revisions: (1) the MN5008 is rated for 17-18 in props, so the baseline moves to 18x6.1 (hover power 666 W instead of 605 W); (2) 6S2P left only 9% current margin at peak thrust, so the pack goes to 6S3P. Both changes are documented on the Mass Rollup tab. MTOW rises 5.05 -&gt; 5.71 kg; the fleet is still 32% under the cap.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="39" customHeight="1" s="36">
       <c r="B12" s="39" t="inlineStr">
         <is>
+          <t>PRICES</t>
+        </is>
+      </c>
+      <c r="C12" s="40" t="inlineStr">
+        <is>
+          <t>INDICATIVE BUDGETARY ESTIMATES IN INR, for planning only. They are not quotations. Import duty, GST and freight are added as separate lines on the Cost Summary. Re-price everything at the Phase 1 procurement gate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="39" t="inlineStr">
+        <is>
+          <t>MASSES</t>
+        </is>
+      </c>
+      <c r="C13" s="40" t="inlineStr">
+        <is>
+          <t>Manufacturer figures where published (marked in the Source column); otherwise engineering estimates. Weigh every part on arrival and update the Actual Mass column — the fleet weigh-in is a pass/fail rule check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="36">
+      <c r="B14" s="39" t="inlineStr">
+        <is>
+          <t>HOW TO USE</t>
+        </is>
+      </c>
+      <c r="C14" s="40" t="inlineStr">
+        <is>
+          <t>Blue cells are inputs you should edit. Black cells are formulas. Yellow cells are decisions still open. Fill the "Actual Mass" and "Actual Price" columns as parts arrive; the Mass Rollup and Cost Summary update automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="36">
+      <c r="B15" s="39" t="inlineStr">
+        <is>
+          <t>TIERS</t>
+        </is>
+      </c>
+      <c r="C15" s="40" t="inlineStr">
+        <is>
+          <t>Where a component has a wide price range (mesh radio, compute, GNSS), three options are listed: A = student budget, B = mid, C = professional. Tier A is costed in the totals. Swapping tiers only requires changing the Include column to 1/0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="36">
+      <c r="B16" s="39" t="inlineStr">
+        <is>
           <t>OPEN DECISIONS</t>
         </is>
       </c>
-      <c r="C12" s="40" t="inlineStr">
+      <c r="C16" s="40" t="inlineStr">
         <is>
           <t>Highlighted yellow: quad vs hex, rolling vs global shutter camera, mesh radio tier, whether an RTK base is permitted by the organisers (see clarification question 1 in the Development Plan).</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="36">
-      <c r="B14" s="41" t="inlineStr">
+    <row r="17" ht="15" customHeight="1" s="36"/>
+    <row r="18" ht="15" customHeight="1" s="36">
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>TAB GUIDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="36">
-      <c r="B15" s="42" t="inlineStr">
-        <is>
-          <t>01 Air Vehicle BOM</t>
-        </is>
-      </c>
-      <c r="C15" s="42" t="inlineStr">
-        <is>
-          <t>Everything on one aircraft. Multiply by 3 for the fleet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="36">
-      <c r="B16" s="42" t="inlineStr">
-        <is>
-          <t>02 Payload &amp; Kits</t>
-        </is>
-      </c>
-      <c r="C16" s="42" t="inlineStr">
-        <is>
-          <t>Survivor kits and the release mechanism, fleet quantities.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="36">
-      <c r="B17" s="42" t="inlineStr">
-        <is>
-          <t>03 Ground Segment</t>
-        </is>
-      </c>
-      <c r="C17" s="42" t="inlineStr">
-        <is>
-          <t>GCS, mesh ground node, RTK base, field infrastructure, safety.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="36">
-      <c r="B18" s="42" t="inlineStr">
-        <is>
-          <t>04 Test &amp; Lab Equipment</t>
-        </is>
-      </c>
-      <c r="C18" s="42" t="inlineStr">
-        <is>
-          <t>Thrust stand, chargers, instruments, calibration targets.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="36">
       <c r="B19" s="42" t="inlineStr">
         <is>
-          <t>05 Spares &amp; Consumables</t>
+          <t>01 Air Vehicle BOM</t>
         </is>
       </c>
       <c r="C19" s="42" t="inlineStr">
         <is>
-          <t>What you must have in the field box and on the bench.</t>
+          <t>Everything on one aircraft. Multiply by 3 for the fleet.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="36">
       <c r="B20" s="42" t="inlineStr">
         <is>
-          <t>06 Software &amp; Data</t>
+          <t>02 Payload &amp; Kits</t>
         </is>
       </c>
       <c r="C20" s="42" t="inlineStr">
         <is>
-          <t>Toolchain, datasets, services. Mostly free — listed so nothing is forgotten.</t>
+          <t>Survivor kits and the release mechanism, fleet quantities.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="36">
       <c r="B21" s="42" t="inlineStr">
         <is>
-          <t>07 Mass Rollup</t>
+          <t>03 Ground Segment</t>
         </is>
       </c>
       <c r="C21" s="42" t="inlineStr">
         <is>
-          <t>Per-aircraft and fleet mass, checked against the 25 kg rule.</t>
+          <t>GCS, mesh ground node, RTK base, field infrastructure, safety.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="36">
       <c r="B22" s="42" t="inlineStr">
         <is>
+          <t>04 Test &amp; Lab Equipment</t>
+        </is>
+      </c>
+      <c r="C22" s="42" t="inlineStr">
+        <is>
+          <t>Thrust stand, chargers, instruments, calibration targets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="42" t="inlineStr">
+        <is>
+          <t>05 Spares &amp; Consumables</t>
+        </is>
+      </c>
+      <c r="C23" s="42" t="inlineStr">
+        <is>
+          <t>What you must have in the field box and on the bench.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="42" t="inlineStr">
+        <is>
+          <t>06 Software &amp; Data</t>
+        </is>
+      </c>
+      <c r="C24" s="42" t="inlineStr">
+        <is>
+          <t>Toolchain, datasets, services. Mostly free — listed so nothing is forgotten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="42" t="inlineStr">
+        <is>
+          <t>07 Mass Rollup</t>
+        </is>
+      </c>
+      <c r="C25" s="42" t="inlineStr">
+        <is>
+          <t>Per-aircraft and fleet mass, checked against the 25 kg rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="42" t="inlineStr">
+        <is>
           <t>08 Cost Summary</t>
         </is>
       </c>
-      <c r="C22" s="42" t="inlineStr">
+      <c r="C26" s="42" t="inlineStr">
         <is>
           <t>Programme cost by category, with duty/GST/freight and contingency.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J3"/>
+  </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4006,111 +4052,111 @@
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="36">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="35" t="inlineStr">
         <is>
           <t>SAFETY — recovery parachute (SYS-41)</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
+      <c r="A67" s="35" t="n">
         <v>56</v>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="35" t="inlineStr">
         <is>
           <t>Recovery parachute</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="35" t="inlineStr">
         <is>
           <t>Ballistic/CO2 or spring canopy for 6 kg AUW, &lt;20 m deployment</t>
         </is>
       </c>
-      <c r="D67" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" t="n">
+      <c r="D67" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" s="35" t="n">
         <v>240</v>
       </c>
-      <c r="F67">
+      <c r="F67" s="35">
         <f>D67*E67</f>
         <v/>
       </c>
-      <c r="G67" t="n">
+      <c r="G67" s="35" t="n">
         <v>12000</v>
       </c>
-      <c r="H67">
+      <c r="H67" s="35">
         <f>D67*G67</f>
         <v/>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="J67" s="35" t="inlineStr">
         <is>
           <t>UAV parachute supplier</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="K67" s="35" t="inlineStr">
         <is>
           <t>3-4 wk</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="L67" s="35" t="inlineStr">
         <is>
           <t>SYS-41. Organisers confirmed a recovery parachute is permitted, ballistic/CO2 included. A crash costs -50; landing outside the pad costs -10, so deploying is worth ~40 points even accepting the penalty. Armed above 20 m, inhibited below (it cannot inflate lower).</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="M67" s="35" t="inlineStr">
         <is>
           <t>Spring-deployed unit if pyro is restricted</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
+      <c r="A68" s="35" t="n">
         <v>57</v>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="35" t="inlineStr">
         <is>
           <t>Parachute mount + bridle</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="35" t="inlineStr">
         <is>
           <t>Top-centre mount, Kevlar bridle, clear deployment cone</t>
         </is>
       </c>
-      <c r="D68" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" t="n">
+      <c r="D68" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="35" t="n">
         <v>60</v>
       </c>
-      <c r="F68">
+      <c r="F68" s="35">
         <f>D68*E68</f>
         <v/>
       </c>
-      <c r="G68" t="n">
+      <c r="G68" s="35" t="n">
         <v>1500</v>
       </c>
-      <c r="H68">
+      <c r="H68" s="35">
         <f>D68*G68</f>
         <v/>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="J68" s="35" t="inlineStr">
         <is>
           <t>In-house</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="K68" s="35" t="inlineStr">
         <is>
           <t>1 wk</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="L68" s="35" t="inlineStr">
         <is>
           <t>Must be designed into the frame, not retrofitted: a bolted-on mount fouls a prop or fires into an arm. Top-centre, clear deployment cone. See frame-design-constraints.md item 5.</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="M68" s="35" t="inlineStr">
         <is>
           <t>None</t>
         </is>
